--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T13:55:49+00:00</t>
+    <t>2026-09-21T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T11:37:47+00:00</t>
+    <t>2026-09-22T11:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T11:13:44+00:00</t>
+    <t>2026-09-23T05:33:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T05:33:05+00:00</t>
+    <t>2026-09-23T16:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:50:58+00:00</t>
+    <t>2026-09-23T17:09:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T17:09:41+00:00</t>
+    <t>2026-09-24T11:03:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:03:30+00:00</t>
+    <t>2026-09-24T15:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T15:40:45+00:00</t>
+    <t>2026-09-25T14:56:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T14:56:10+00:00</t>
+    <t>2026-09-29T10:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:09:39+00:00</t>
+    <t>2026-09-29T10:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T10:46:32+00:00</t>
+    <t>2026-09-29T11:13:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T11:13:32+00:00</t>
+    <t>2026-09-29T15:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T15:22:43+00:00</t>
+    <t>2026-09-30T17:01:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T17:01:19+00:00</t>
+    <t>2026-09-30T18:21:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T18:21:17+00:00</t>
+    <t>2026-10-01T11:37:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:37:05+00:00</t>
+    <t>2026-10-01T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:47:48+00:00</t>
+    <t>2026-10-01T21:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T21:19:24+00:00</t>
+    <t>2026-10-02T13:24:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$33</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="245">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T13:24:17+00:00</t>
+    <t>2026-10-07T12:50:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,6 +439,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>IVL(TS) used in a QSI</t>
   </si>
   <si>
@@ -517,6 +520,26 @@
   </si>
   <si>
     <t>./high</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration</t>
+  </si>
+  <si>
+    <t>boundsDuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange</t>
+  </si>
+  <si>
+    <t>boundsRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
   </si>
   <si>
     <t>Timing.repeat.count</t>
@@ -1078,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AL33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.78125" customWidth="true" bestFit="true"/>
@@ -2288,7 +2311,7 @@
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>130</v>
@@ -2309,18 +2332,18 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>130</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -2342,7 +2365,7 @@
         <v>104</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>132</v>
@@ -2417,15 +2440,15 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2528,10 +2551,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2636,10 +2659,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2665,13 +2688,13 @@
         <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2721,7 +2744,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2730,24 +2753,24 @@
         <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2773,20 +2796,20 @@
         <v>110</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R16" t="s" s="2">
         <v>21</v>
@@ -2831,7 +2854,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2840,26 +2863,28 @@
         <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D17" t="s" s="2">
         <v>21</v>
       </c>
@@ -2880,20 +2905,16 @@
         <v>104</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
       </c>
@@ -2941,7 +2962,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2959,17 +2980,19 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>130</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
@@ -2990,13 +3013,13 @@
         <v>104</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3047,7 +3070,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3065,15 +3088,15 @@
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>167</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3096,19 +3119,19 @@
         <v>104</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3157,7 +3180,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3175,15 +3198,15 @@
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3206,20 +3229,16 @@
         <v>104</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3267,7 +3286,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3285,15 +3304,15 @@
         <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3316,16 +3335,20 @@
         <v>104</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -3349,13 +3372,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>185</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>186</v>
+        <v>21</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -3373,7 +3396,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3391,15 +3414,15 @@
         <v>21</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3422,22 +3445,24 @@
         <v>104</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>187</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q22" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3481,7 +3506,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3499,15 +3524,15 @@
         <v>21</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3530,13 +3555,13 @@
         <v>104</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3563,13 +3588,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>21</v>
+        <v>193</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -3587,7 +3612,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3605,10 +3630,10 @@
         <v>21</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>196</v>
       </c>
@@ -3627,7 +3652,7 @@
         <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -3636,7 +3661,7 @@
         <v>104</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>197</v>
@@ -3649,7 +3674,9 @@
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q24" s="2"/>
+      <c r="Q24" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="R24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3711,15 +3738,15 @@
         <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3742,13 +3769,13 @@
         <v>104</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3799,7 +3826,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3817,15 +3844,15 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" hidden="true">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3839,7 +3866,7 @@
         <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
@@ -3848,13 +3875,13 @@
         <v>104</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3881,11 +3908,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>205</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -3903,7 +3932,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3921,7 +3950,7 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -3940,7 +3969,7 @@
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -3952,7 +3981,7 @@
         <v>104</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>207</v>
@@ -3960,9 +3989,7 @@
       <c r="M27" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -3987,11 +4014,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4015,7 +4044,7 @@
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
@@ -4027,15 +4056,15 @@
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>90</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4046,7 +4075,7 @@
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>21</v>
@@ -4058,17 +4087,15 @@
         <v>104</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4093,13 +4120,11 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>212</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4117,13 +4142,13 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>21</v>
@@ -4135,15 +4160,15 @@
         <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4157,7 +4182,7 @@
         <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4166,20 +4191,18 @@
         <v>104</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
       </c>
@@ -4203,13 +4226,11 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -4227,7 +4248,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4245,15 +4266,15 @@
         <v>21</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4264,10 +4285,10 @@
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -4276,15 +4297,17 @@
         <v>104</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4333,13 +4356,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -4351,15 +4374,15 @@
         <v>21</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" hidden="true">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4370,10 +4393,10 @@
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
@@ -4382,18 +4405,20 @@
         <v>104</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -4417,13 +4442,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>234</v>
+        <v>192</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -4441,13 +4466,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -4459,11 +4484,225 @@
         <v>21</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K33" t="s" s="2">
         <v>237</v>
       </c>
+      <c r="L33" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>244</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL31">
+  <autoFilter ref="A1:AL33">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4473,7 +4712,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI30">
+  <conditionalFormatting sqref="A2:AI32">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T12:50:21+00:00</t>
+    <t>2026-10-07T13:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T13:01:43+00:00</t>
+    <t>2026-10-08T06:44:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T06:44:48+00:00</t>
+    <t>2026-10-08T16:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T16:43:43+00:00</t>
+    <t>2026-10-08T20:06:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T20:06:16+00:00</t>
+    <t>2026-10-09T14:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T14:33:13+00:00</t>
+    <t>2026-10-09T16:18:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T16:18:46+00:00</t>
+    <t>2026-10-12T06:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T06:12:55+00:00</t>
+    <t>2026-10-12T12:45:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:45:08+00:00</t>
+    <t>2026-10-12T17:47:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T17:47:09+00:00</t>
+    <t>2026-10-13T16:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T16:03:24+00:00</t>
+    <t>2026-10-14T07:51:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T07:51:23+00:00</t>
+    <t>2026-10-14T10:33:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:33:13+00:00</t>
+    <t>2026-10-14T18:50:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T18:50:32+00:00</t>
+    <t>2026-10-14T21:19:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T21:19:26+00:00</t>
+    <t>2026-10-15T08:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:30:16+00:00</t>
+    <t>2026-10-15T11:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:48:20+00:00</t>
+    <t>2026-10-15T13:39:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:39:50+00:00</t>
+    <t>2026-10-15T16:16:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:16:55+00:00</t>
+    <t>2026-10-15T16:39:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T16:39:56+00:00</t>
+    <t>2026-10-16T09:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:51:31+00:00</t>
+    <t>2026-10-16T10:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T10:13:15+00:00</t>
+    <t>2026-10-16T11:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:00:25+00:00</t>
+    <t>2026-10-17T00:02:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T00:02:12+00:00</t>
+    <t>2026-10-17T19:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-17T19:55:22+00:00</t>
+    <t>2026-10-18T08:01:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T08:01:40+00:00</t>
+    <t>2026-10-18T09:33:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$58</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="337">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T09:33:28+00:00</t>
+    <t>2026-10-18T20:24:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -335,21 +335,13 @@
     <t>Timing.modifierExtension</t>
   </si>
   <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Fachliche Begründung: Für den Medikationsplan sind keine zusätzlichen Erweiterungen vorgesehen, die die Bedeutung der Ressource oder ihrer Elemente verändern.</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
@@ -362,7 +354,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitpunkt der Einnahme.</t>
+    <t>Event im Alltag des Patienten auf das sich das Timing bezieht z.b. OP-Termin</t>
   </si>
   <si>
     <t>Identifies specific times when the event occurs.</t>
@@ -381,7 +373,7 @@
 </t>
   </si>
   <si>
-    <t>Wiederholungsangaben zur Einnahme</t>
+    <t>Wiederholungsangaben des Timings</t>
   </si>
   <si>
     <t>A set of rules that describe when the event is scheduled.</t>
@@ -473,7 +465,7 @@
     <t>Timing.repeat.bounds[x].start</t>
   </si>
   <si>
-    <t>Zeitraum der Einnahme: Start.</t>
+    <t>Start des Begrenzungszeitraums</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
@@ -501,7 +493,7 @@
     <t>Timing.repeat.bounds[x].end</t>
   </si>
   <si>
-    <t>Zeitraum der Einnahme: Ende.</t>
+    <t>Ende des Begrenzungszeitraums</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
@@ -532,6 +524,160 @@
 </t>
   </si>
   <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.value</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.comparator</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].comparator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Fachliche Begründung: TODO</t>
+  </si>
+  <si>
+    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.unit</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.system</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsDuration.code</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
+  </si>
+  <si>
     <t>Timing.repeat.bounds[x]:boundsRange</t>
   </si>
   <si>
@@ -542,6 +688,149 @@
 </t>
   </si>
   <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+</t>
+  </si>
+  <si>
+    <t>Low limit</t>
+  </si>
+  <si>
+    <t>The low limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the low element is missing, the low boundary is not known.</t>
+  </si>
+  <si>
+    <t>Range.low</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
+    <t>NR.1</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.value</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.value</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.comparator</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.comparator</t>
+  </si>
+  <si>
+    <t>Not allowed to be used in this context</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.unit</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.unit</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.system</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.system</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.low.code</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].low.code</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high</t>
+  </si>
+  <si>
+    <t>High limit</t>
+  </si>
+  <si>
+    <t>The high limit. The boundary is inclusive.</t>
+  </si>
+  <si>
+    <t>If the high element is missing, the high boundary is not known.</t>
+  </si>
+  <si>
+    <t>Range.high</t>
+  </si>
+  <si>
+    <t>NR.2</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.id</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.extension</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.value</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.value</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.comparator</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.comparator</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.unit</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.unit</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.system</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.system</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x]:boundsRange.high.code</t>
+  </si>
+  <si>
+    <t>Timing.repeat.bounds[x].high.code</t>
+  </si>
+  <si>
     <t>Timing.repeat.count</t>
   </si>
   <si>
@@ -576,10 +865,6 @@
     <t>Timing.repeat.duration</t>
   </si>
   <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
     <t>How long when it happens</t>
   </si>
   <si>
@@ -607,17 +892,10 @@
     <t>Timing.repeat.durationUnit</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>s | min | h | d | wk | mo | a - unit of time (UCUM)</t>
   </si>
   <si>
     <t>The units of time for the duration, in UCUM units.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>A unit of time (units from UCUM).</t>
@@ -1101,24 +1379,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL33"/>
+  <dimension ref="A1:AL58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.78125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.5234375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.2265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.9140625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="16.07421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="26.30078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="26.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="120.28125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1128,7 +1406,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="34.453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="46.3671875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="48.484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1140,7 +1418,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="59.11328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1590,39 +1868,35 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>105</v>
       </c>
-      <c r="M5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
       </c>
@@ -1670,7 +1944,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1688,15 +1962,15 @@
         <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>82</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1710,26 +1984,26 @@
         <v>76</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>21</v>
@@ -1778,7 +2052,7 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>75</v>
@@ -1796,15 +2070,15 @@
         <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1818,26 +2092,26 @@
         <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>21</v>
@@ -1886,7 +2160,7 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1898,21 +2172,21 @@
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2015,10 +2289,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2123,13 +2397,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="C10" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -2142,7 +2416,7 @@
         <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
@@ -2151,16 +2425,16 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2233,10 +2507,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2250,22 +2524,22 @@
         <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>131</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2304,17 +2578,17 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2332,18 +2606,18 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>136</v>
-      </c>
-    </row>
-    <row r="12" hidden="true">
-      <c r="A12" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -2356,22 +2630,22 @@
         <v>85</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2422,7 +2696,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2440,15 +2714,15 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2551,10 +2825,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2657,12 +2931,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2676,25 +2950,25 @@
         <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2744,7 +3018,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2753,24 +3027,24 @@
         <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="B16" t="s" s="2">
         <v>152</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
-      <c r="A16" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2784,32 +3058,32 @@
         <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q16" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R16" t="s" s="2">
         <v>21</v>
@@ -2854,7 +3128,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2863,27 +3137,27 @@
         <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="B17" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C17" t="s" s="2">
         <v>161</v>
-      </c>
-    </row>
-    <row r="17" hidden="true">
-      <c r="A17" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>21</v>
@@ -2896,22 +3170,22 @@
         <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2962,7 +3236,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2980,19 +3254,17 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3010,16 +3282,16 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3070,7 +3342,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3082,32 +3354,32 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>136</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3116,23 +3388,21 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>170</v>
+        <v>94</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3168,45 +3438,45 @@
         <v>21</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" hidden="true">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3214,31 +3484,35 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3286,7 +3560,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3301,7 +3575,7 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>174</v>
@@ -3309,10 +3583,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3323,62 +3597,62 @@
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" s="2"/>
+      <c r="O21" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="P21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q21" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="R21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X21" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="O21" t="s" s="2">
+      <c r="Y21" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="P21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q21" s="2"/>
-      <c r="R21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="Z21" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -3396,7 +3670,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3411,18 +3685,18 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3430,34 +3704,32 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3506,7 +3778,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3521,18 +3793,18 @@
         <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3540,31 +3812,33 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+      <c r="O23" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3588,13 +3862,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>193</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -3612,7 +3886,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3621,24 +3895,24 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3646,37 +3920,39 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q24" t="s" s="2">
-        <v>199</v>
-      </c>
+      <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3720,7 +3996,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3735,20 +4011,22 @@
         <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>128</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3760,22 +4038,22 @@
         <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3826,7 +4104,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>200</v>
+        <v>128</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3844,15 +4122,15 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3866,22 +4144,22 @@
         <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>179</v>
+        <v>86</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>204</v>
+        <v>87</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>205</v>
+        <v>88</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3932,7 +4210,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>203</v>
+        <v>89</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3944,32 +4222,32 @@
         <v>21</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>184</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
@@ -3978,18 +4256,20 @@
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4026,45 +4306,45 @@
         <v>21</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>206</v>
+        <v>100</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4078,24 +4358,26 @@
         <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4120,11 +4402,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4142,7 +4426,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4154,21 +4438,21 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>195</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4179,7 +4463,7 @@
         <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4188,20 +4472,18 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>214</v>
+        <v>87</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4226,11 +4508,13 @@
         <v>21</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>217</v>
+        <v>21</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>21</v>
@@ -4248,19 +4532,19 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>89</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>21</v>
@@ -4271,14 +4555,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4294,19 +4578,19 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>219</v>
+        <v>93</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>94</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4344,19 +4628,19 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>218</v>
+        <v>100</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4368,7 +4652,7 @@
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>21</v>
@@ -4379,10 +4663,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4390,34 +4674,34 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -4442,13 +4726,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>228</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -4466,13 +4750,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -4481,18 +4765,18 @@
         <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4503,32 +4787,36 @@
         <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>104</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>232</v>
+        <v>177</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>233</v>
+        <v>178</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="Q32" s="2"/>
+      <c r="Q32" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="R32" t="s" s="2">
         <v>21</v>
       </c>
@@ -4548,13 +4836,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -4572,7 +4860,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4587,18 +4875,18 @@
         <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>21</v>
+        <v>186</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>236</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4606,33 +4894,33 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>237</v>
+        <v>86</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>238</v>
+        <v>190</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
       </c>
@@ -4656,13 +4944,13 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>21</v>
@@ -4680,7 +4968,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4695,14 +4983,2710 @@
         <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>244</v>
       </c>
+      <c r="M36" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q40" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q49" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="R49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y53" s="2"/>
+      <c r="Z53" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y54" s="2"/>
+      <c r="Z54" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL33">
+  <autoFilter ref="A1:AL58">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4712,7 +7696,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI32">
+  <conditionalFormatting sqref="A2:AI57">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-18T20:24:08+00:00</t>
+    <t>2026-10-19T15:55:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:55:36+00:00</t>
+    <t>2026-10-19T16:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T16:11:48+00:00</t>
+    <t>2026-10-19T18:28:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T18:28:35+00:00</t>
+    <t>2026-10-20T08:04:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T08:04:36+00:00</t>
+    <t>2026-10-20T12:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T12:30:11+00:00</t>
+    <t>2026-10-20T15:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T15:36:59+00:00</t>
+    <t>2026-10-20T16:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T16:38:16+00:00</t>
+    <t>2026-10-20T17:05:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-20T17:05:58+00:00</t>
+    <t>2026-10-21T09:29:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:29:04+00:00</t>
+    <t>2026-10-21T09:52:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:38+00:00</t>
+    <t>2026-10-21T10:08:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T10:08:52+00:00</t>
+    <t>2026-10-21T11:24:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T11:24:22+00:00</t>
+    <t>2026-10-21T12:17:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T12:17:05+00:00</t>
+    <t>2026-10-21T14:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T14:17:59+00:00</t>
+    <t>2026-10-21T15:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:07:55+00:00</t>
+    <t>2026-10-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T15:51:37+00:00</t>
+    <t>2026-10-22T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:17:51+00:00</t>
+    <t>2026-10-22T07:44:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T07:44:55+00:00</t>
+    <t>2026-10-22T08:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T08:46:49+00:00</t>
+    <t>2026-10-22T09:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:37:30+00:00</t>
+    <t>2026-10-22T09:48:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T09:48:24+00:00</t>
+    <t>2026-10-22T11:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T11:28:40+00:00</t>
+    <t>2026-10-22T12:03:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:03:52+00:00</t>
+    <t>2026-10-22T12:14:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T12:14:48+00:00</t>
+    <t>2026-10-22T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-22T18:22:51+00:00</t>
+    <t>2026-10-23T11:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T11:54:03+00:00</t>
+    <t>2026-10-23T12:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T12:23:07+00:00</t>
+    <t>2026-10-23T13:54:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T13:54:21+00:00</t>
+    <t>2026-10-23T16:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T16:16:05+00:00</t>
+    <t>2026-10-26T11:42:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T11:42:48+00:00</t>
+    <t>2026-10-26T12:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T12:04:07+00:00</t>
+    <t>2026-10-26T13:41:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:41:17+00:00</t>
+    <t>2026-10-26T13:57:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T13:57:36+00:00</t>
+    <t>2026-10-26T16:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:01:21+00:00</t>
+    <t>2026-10-26T16:19:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T16:19:19+00:00</t>
+    <t>2026-10-26T17:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:11:45+00:00</t>
+    <t>2026-10-26T17:20:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:20:41+00:00</t>
+    <t>2026-10-26T17:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T17:56:13+00:00</t>
+    <t>2026-10-26T18:36:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T18:36:30+00:00</t>
+    <t>2026-10-26T20:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:24:37+00:00</t>
+    <t>2026-10-26T20:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T20:58:24+00:00</t>
+    <t>2026-10-26T21:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-26T21:10:14+00:00</t>
+    <t>2026-10-27T12:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:33:12+00:00</t>
+    <t>2026-10-27T12:53:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T12:53:20+00:00</t>
+    <t>2026-10-27T13:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:46:50+00:00</t>
+    <t>2026-10-27T19:38:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T19:38:06+00:00</t>
+    <t>2026-10-27T20:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T20:05:18+00:00</t>
+    <t>2026-10-27T21:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T21:19:55+00:00</t>
+    <t>2026-10-28T09:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T09:21:39+00:00</t>
+    <t>2026-10-28T10:28:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T10:28:56+00:00</t>
+    <t>2026-10-28T15:47:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T15:47:56+00:00</t>
+    <t>2026-10-28T21:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T21:33:03+00:00</t>
+    <t>2026-10-29T07:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:35:42+00:00</t>
+    <t>2026-10-29T08:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:12:50+00:00</t>
+    <t>2026-10-29T08:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T08:46:29+00:00</t>
+    <t>2026-10-29T10:03:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:03:24+00:00</t>
+    <t>2026-10-29T10:46:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T10:46:22+00:00</t>
+    <t>2026-10-29T11:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="338">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T11:16:49+00:00</t>
+    <t>2026-10-29T12:53:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>Timing.repeat.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
   </si>
   <si>
     <t>Timing.repeat.extension:TimingDayOfMonth</t>
@@ -2296,7 +2299,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2306,7 +2309,7 @@
         <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>21</v>
@@ -2318,14 +2321,12 @@
         <v>93</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>96</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2392,18 +2393,18 @@
         <v>21</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
@@ -2425,16 +2426,16 @@
         <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2507,10 +2508,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2533,13 +2534,13 @@
         <v>103</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2578,17 +2579,17 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2606,18 +2607,18 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
@@ -2639,13 +2640,13 @@
         <v>103</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2696,7 +2697,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2714,15 +2715,15 @@
         <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2825,10 +2826,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2933,10 +2934,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2962,13 +2963,13 @@
         <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3018,7 +3019,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3027,24 +3028,24 @@
         <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3070,20 +3071,20 @@
         <v>108</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q16" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R16" t="s" s="2">
         <v>21</v>
@@ -3128,7 +3129,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3137,27 +3138,27 @@
         <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>21</v>
@@ -3179,13 +3180,13 @@
         <v>103</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3236,7 +3237,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3254,15 +3255,15 @@
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3365,10 +3366,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3473,10 +3474,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3499,19 +3500,19 @@
         <v>103</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3560,7 +3561,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3575,18 +3576,18 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3609,23 +3610,23 @@
         <v>103</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>21</v>
@@ -3646,13 +3647,13 @@
         <v>21</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>21</v>
@@ -3670,7 +3671,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3685,18 +3686,18 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3722,14 +3723,14 @@
         <v>86</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3778,7 +3779,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3793,18 +3794,18 @@
         <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3827,17 +3828,17 @@
         <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3886,7 +3887,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3895,24 +3896,24 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3935,19 +3936,19 @@
         <v>103</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -3996,7 +3997,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4011,21 +4012,21 @@
         <v>81</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>21</v>
@@ -4047,13 +4048,13 @@
         <v>103</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4104,7 +4105,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4122,15 +4123,15 @@
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4233,10 +4234,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4341,10 +4342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4367,16 +4368,16 @@
         <v>103</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4426,7 +4427,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4438,21 +4439,21 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4555,10 +4556,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4663,10 +4664,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4689,19 +4690,19 @@
         <v>103</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -4750,7 +4751,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4765,18 +4766,18 @@
         <v>81</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4799,23 +4800,23 @@
         <v>103</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R32" t="s" s="2">
         <v>21</v>
@@ -4836,13 +4837,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -4860,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4875,18 +4876,18 @@
         <v>81</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4912,14 +4913,14 @@
         <v>86</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -4968,7 +4969,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4983,18 +4984,18 @@
         <v>81</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5017,17 +5018,17 @@
         <v>103</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -5076,7 +5077,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5085,24 +5086,24 @@
         <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5125,19 +5126,19 @@
         <v>103</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5186,7 +5187,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5201,18 +5202,18 @@
         <v>81</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5235,16 +5236,16 @@
         <v>103</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5294,7 +5295,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5306,21 +5307,21 @@
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5423,10 +5424,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5531,10 +5532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5557,19 +5558,19 @@
         <v>103</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -5618,7 +5619,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -5633,18 +5634,18 @@
         <v>81</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5667,23 +5668,23 @@
         <v>103</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>21</v>
@@ -5704,13 +5705,13 @@
         <v>21</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>21</v>
@@ -5728,7 +5729,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5743,18 +5744,18 @@
         <v>81</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5780,14 +5781,14 @@
         <v>86</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -5836,7 +5837,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5851,18 +5852,18 @@
         <v>81</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5885,17 +5886,17 @@
         <v>103</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -5944,7 +5945,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -5953,24 +5954,24 @@
         <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5993,19 +5994,19 @@
         <v>103</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6054,7 +6055,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6069,18 +6070,18 @@
         <v>81</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6103,19 +6104,19 @@
         <v>103</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6164,7 +6165,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6182,15 +6183,15 @@
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6213,13 +6214,13 @@
         <v>103</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6270,7 +6271,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6288,15 +6289,15 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6319,19 +6320,19 @@
         <v>103</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -6380,7 +6381,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6398,15 +6399,15 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6429,19 +6430,19 @@
         <v>103</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -6490,7 +6491,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -6508,15 +6509,15 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6539,13 +6540,13 @@
         <v>103</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6572,13 +6573,13 @@
         <v>21</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>21</v>
@@ -6596,7 +6597,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6614,15 +6615,15 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6645,13 +6646,13 @@
         <v>103</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6659,7 +6660,7 @@
         <v>21</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>21</v>
@@ -6704,7 +6705,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -6722,15 +6723,15 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6753,13 +6754,13 @@
         <v>103</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6810,7 +6811,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -6828,15 +6829,15 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6859,13 +6860,13 @@
         <v>103</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6916,7 +6917,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -6934,15 +6935,15 @@
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6965,13 +6966,13 @@
         <v>103</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7022,7 +7023,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7040,15 +7041,15 @@
         <v>21</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7071,13 +7072,13 @@
         <v>103</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7104,11 +7105,11 @@
         <v>21</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>21</v>
@@ -7126,7 +7127,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7144,15 +7145,15 @@
         <v>21</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7175,16 +7176,16 @@
         <v>103</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7210,11 +7211,11 @@
         <v>21</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>21</v>
@@ -7232,7 +7233,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7255,10 +7256,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7281,16 +7282,16 @@
         <v>103</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7340,7 +7341,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -7363,10 +7364,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7389,19 +7390,19 @@
         <v>103</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>21</v>
@@ -7426,13 +7427,13 @@
         <v>21</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -7450,7 +7451,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7468,15 +7469,15 @@
         <v>21</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7499,13 +7500,13 @@
         <v>103</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7556,7 +7557,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7574,15 +7575,15 @@
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7605,16 +7606,16 @@
         <v>103</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7640,13 +7641,13 @@
         <v>21</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>21</v>
@@ -7664,7 +7665,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -7682,7 +7683,7 @@
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T12:53:50+00:00</t>
+    <t>2026-10-29T13:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:18:54+00:00</t>
+    <t>2026-10-29T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T13:53:17+00:00</t>
+    <t>2026-10-29T14:20:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -574,7 +574,7 @@
 </t>
   </si>
   <si>
-    <t>Fachliche Begründung: TODO</t>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-timing.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T14:20:15+00:00</t>
+    <t>2026-10-29T14:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
